--- a/tools/synthetic_pilots/synth_fmcg_brand.xlsx
+++ b/tools/synthetic_pilots/synth_fmcg_brand.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Данные" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
     <t>price_index</t>
   </si>
   <si>
-    <t>holiday_newyear_preshop</t>
+    <t>holiday_newyear</t>
   </si>
 </sst>
 </file>
@@ -413,22 +413,22 @@
         <v>44957</v>
       </c>
       <c r="B2">
-        <v>24251737</v>
+        <v>25918151</v>
       </c>
       <c r="C2">
-        <v>10298985</v>
+        <v>14862041</v>
       </c>
       <c r="D2">
-        <v>3429808</v>
+        <v>4194280</v>
       </c>
       <c r="E2">
-        <v>104.6</v>
+        <v>144.3</v>
       </c>
       <c r="F2">
-        <v>328175</v>
+        <v>949391</v>
       </c>
       <c r="G2">
-        <v>211.9</v>
+        <v>239.6</v>
       </c>
       <c r="H2">
         <v>1.007</v>
@@ -442,22 +442,22 @@
         <v>44985</v>
       </c>
       <c r="B3">
-        <v>24464405</v>
+        <v>24522226</v>
       </c>
       <c r="C3">
-        <v>8503057</v>
+        <v>6079740</v>
       </c>
       <c r="D3">
-        <v>4026311</v>
+        <v>2258843</v>
       </c>
       <c r="E3">
-        <v>161.7</v>
+        <v>242.9</v>
       </c>
       <c r="F3">
-        <v>310014</v>
+        <v>383814</v>
       </c>
       <c r="G3">
-        <v>175.4</v>
+        <v>196.8</v>
       </c>
       <c r="H3">
         <v>1.0087</v>
@@ -471,22 +471,22 @@
         <v>45016</v>
       </c>
       <c r="B4">
-        <v>25459504</v>
+        <v>24738506</v>
       </c>
       <c r="C4">
-        <v>12727101</v>
+        <v>9020060</v>
       </c>
       <c r="D4">
-        <v>4565018</v>
+        <v>5382123</v>
       </c>
       <c r="E4">
-        <v>146.5</v>
+        <v>166.9</v>
       </c>
       <c r="F4">
-        <v>480019</v>
+        <v>903041</v>
       </c>
       <c r="G4">
-        <v>205.1</v>
+        <v>269.8</v>
       </c>
       <c r="H4">
         <v>0.9752</v>
@@ -500,22 +500,22 @@
         <v>45046</v>
       </c>
       <c r="B5">
-        <v>25981471</v>
+        <v>25566055</v>
       </c>
       <c r="C5">
-        <v>13681804</v>
+        <v>12148307</v>
       </c>
       <c r="D5">
-        <v>6384583</v>
+        <v>7468711</v>
       </c>
       <c r="E5">
-        <v>67.59999999999999</v>
+        <v>56.8</v>
       </c>
       <c r="F5">
-        <v>389447</v>
+        <v>388823</v>
       </c>
       <c r="G5">
-        <v>172.1</v>
+        <v>168.5</v>
       </c>
       <c r="H5">
         <v>0.9972</v>
@@ -529,22 +529,22 @@
         <v>45077</v>
       </c>
       <c r="B6">
-        <v>26884893</v>
+        <v>25592698</v>
       </c>
       <c r="C6">
-        <v>7659463</v>
+        <v>5856435</v>
       </c>
       <c r="D6">
-        <v>5613298</v>
+        <v>5211729</v>
       </c>
       <c r="E6">
-        <v>282.7</v>
+        <v>434.7</v>
       </c>
       <c r="F6">
-        <v>703535</v>
+        <v>1238455</v>
       </c>
       <c r="G6">
-        <v>216.9</v>
+        <v>245.2</v>
       </c>
       <c r="H6">
         <v>0.9976</v>
@@ -558,22 +558,22 @@
         <v>45107</v>
       </c>
       <c r="B7">
-        <v>28839211</v>
+        <v>27192806</v>
       </c>
       <c r="C7">
-        <v>14342654</v>
+        <v>14724316</v>
       </c>
       <c r="D7">
-        <v>6419192</v>
+        <v>4361525</v>
       </c>
       <c r="E7">
-        <v>288.2</v>
+        <v>391.8</v>
       </c>
       <c r="F7">
-        <v>227751</v>
+        <v>114537</v>
       </c>
       <c r="G7">
-        <v>61</v>
+        <v>63.7</v>
       </c>
       <c r="H7">
         <v>1.0143</v>
@@ -587,22 +587,22 @@
         <v>45138</v>
       </c>
       <c r="B8">
-        <v>28277321</v>
+        <v>26671372</v>
       </c>
       <c r="C8">
-        <v>9640641</v>
+        <v>8828391</v>
       </c>
       <c r="D8">
-        <v>6344366</v>
+        <v>7137048</v>
       </c>
       <c r="E8">
-        <v>117.3</v>
+        <v>179.2</v>
       </c>
       <c r="F8">
-        <v>489777</v>
+        <v>496361</v>
       </c>
       <c r="G8">
-        <v>102.1</v>
+        <v>67.8</v>
       </c>
       <c r="H8">
         <v>1.0333</v>
@@ -616,22 +616,22 @@
         <v>45169</v>
       </c>
       <c r="B9">
-        <v>27024897</v>
+        <v>26611156</v>
       </c>
       <c r="C9">
-        <v>9134335</v>
+        <v>11794484</v>
       </c>
       <c r="D9">
-        <v>4898716</v>
+        <v>4574456</v>
       </c>
       <c r="E9">
-        <v>185.1</v>
+        <v>259</v>
       </c>
       <c r="F9">
-        <v>449013</v>
+        <v>741485</v>
       </c>
       <c r="G9">
-        <v>107.9</v>
+        <v>144</v>
       </c>
       <c r="H9">
         <v>0.9721</v>
@@ -645,22 +645,22 @@
         <v>45199</v>
       </c>
       <c r="B10">
-        <v>26225204</v>
+        <v>26275080</v>
       </c>
       <c r="C10">
-        <v>4415694</v>
+        <v>5321382</v>
       </c>
       <c r="D10">
-        <v>7152354</v>
+        <v>8434457</v>
       </c>
       <c r="E10">
-        <v>70.8</v>
+        <v>53.1</v>
       </c>
       <c r="F10">
-        <v>339150</v>
+        <v>319138</v>
       </c>
       <c r="G10">
-        <v>135</v>
+        <v>118.1</v>
       </c>
       <c r="H10">
         <v>1.0007</v>
@@ -674,22 +674,22 @@
         <v>45230</v>
       </c>
       <c r="B11">
-        <v>25342609</v>
+        <v>25267923</v>
       </c>
       <c r="C11">
-        <v>5831694</v>
+        <v>8546610</v>
       </c>
       <c r="D11">
-        <v>3839055</v>
+        <v>4028072</v>
       </c>
       <c r="E11">
-        <v>145.8</v>
+        <v>122.6</v>
       </c>
       <c r="F11">
-        <v>177437</v>
+        <v>272947</v>
       </c>
       <c r="G11">
-        <v>87.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11">
         <v>1.0494</v>
@@ -703,22 +703,22 @@
         <v>45260</v>
       </c>
       <c r="B12">
-        <v>25968924</v>
+        <v>25749963</v>
       </c>
       <c r="C12">
-        <v>6112129</v>
+        <v>12778437</v>
       </c>
       <c r="D12">
-        <v>3362922</v>
+        <v>4643357</v>
       </c>
       <c r="E12">
-        <v>109.3</v>
+        <v>182.2</v>
       </c>
       <c r="F12">
-        <v>228716</v>
+        <v>424393</v>
       </c>
       <c r="G12">
-        <v>95.59999999999999</v>
+        <v>135.9</v>
       </c>
       <c r="H12">
         <v>0.9832</v>
@@ -732,22 +732,22 @@
         <v>45291</v>
       </c>
       <c r="B13">
-        <v>25177824</v>
+        <v>26692485</v>
       </c>
       <c r="C13">
-        <v>12331417</v>
+        <v>18358911</v>
       </c>
       <c r="D13">
-        <v>3408948</v>
+        <v>3286071</v>
       </c>
       <c r="E13">
-        <v>173.8</v>
+        <v>311.1</v>
       </c>
       <c r="F13">
-        <v>323332</v>
+        <v>462790</v>
       </c>
       <c r="G13">
-        <v>136.5</v>
+        <v>163.5</v>
       </c>
       <c r="H13">
         <v>0.9814000000000001</v>
@@ -761,22 +761,22 @@
         <v>45322</v>
       </c>
       <c r="B14">
-        <v>26365576</v>
+        <v>27404583</v>
       </c>
       <c r="C14">
-        <v>10152503</v>
+        <v>16319427</v>
       </c>
       <c r="D14">
-        <v>6273439</v>
+        <v>5082209</v>
       </c>
       <c r="E14">
-        <v>160.9</v>
+        <v>208.1</v>
       </c>
       <c r="F14">
-        <v>503414</v>
+        <v>523998</v>
       </c>
       <c r="G14">
-        <v>70</v>
+        <v>60.6</v>
       </c>
       <c r="H14">
         <v>1.0127</v>
@@ -790,22 +790,22 @@
         <v>45351</v>
       </c>
       <c r="B15">
-        <v>27959569</v>
+        <v>27555278</v>
       </c>
       <c r="C15">
-        <v>12456848</v>
+        <v>11620659</v>
       </c>
       <c r="D15">
-        <v>5356978</v>
+        <v>6081657</v>
       </c>
       <c r="E15">
-        <v>178.3</v>
+        <v>202.8</v>
       </c>
       <c r="F15">
-        <v>560413</v>
+        <v>734655</v>
       </c>
       <c r="G15">
-        <v>51.9</v>
+        <v>48.1</v>
       </c>
       <c r="H15">
         <v>1.0326</v>
@@ -819,22 +819,22 @@
         <v>45382</v>
       </c>
       <c r="B16">
-        <v>26174613</v>
+        <v>27114305</v>
       </c>
       <c r="C16">
-        <v>10504526</v>
+        <v>8637605</v>
       </c>
       <c r="D16">
-        <v>3848228</v>
+        <v>4229490</v>
       </c>
       <c r="E16">
-        <v>92.2</v>
+        <v>120.4</v>
       </c>
       <c r="F16">
-        <v>385201</v>
+        <v>957536</v>
       </c>
       <c r="G16">
-        <v>126.1</v>
+        <v>140.3</v>
       </c>
       <c r="H16">
         <v>1.0081</v>
@@ -848,22 +848,22 @@
         <v>45412</v>
       </c>
       <c r="B17">
-        <v>26736091</v>
+        <v>27226444</v>
       </c>
       <c r="C17">
-        <v>9108752</v>
+        <v>7113693</v>
       </c>
       <c r="D17">
-        <v>5879355</v>
+        <v>8455362</v>
       </c>
       <c r="E17">
-        <v>228.9</v>
+        <v>174.7</v>
       </c>
       <c r="F17">
-        <v>402880</v>
+        <v>392372</v>
       </c>
       <c r="G17">
-        <v>101.9</v>
+        <v>66.5</v>
       </c>
       <c r="H17">
         <v>1.0482</v>
@@ -877,22 +877,22 @@
         <v>45443</v>
       </c>
       <c r="B18">
-        <v>26309679</v>
+        <v>25946095</v>
       </c>
       <c r="C18">
-        <v>9559211</v>
+        <v>5322795</v>
       </c>
       <c r="D18">
-        <v>3918627</v>
+        <v>4894428</v>
       </c>
       <c r="E18">
-        <v>110.8</v>
+        <v>109.3</v>
       </c>
       <c r="F18">
-        <v>395393</v>
+        <v>804859</v>
       </c>
       <c r="G18">
-        <v>73.3</v>
+        <v>56.5</v>
       </c>
       <c r="H18">
         <v>1.0346</v>
@@ -906,22 +906,22 @@
         <v>45473</v>
       </c>
       <c r="B19">
-        <v>25550183</v>
+        <v>26024034</v>
       </c>
       <c r="C19">
-        <v>6063496</v>
+        <v>4164914</v>
       </c>
       <c r="D19">
-        <v>6597257</v>
+        <v>7946400</v>
       </c>
       <c r="E19">
-        <v>85.7</v>
+        <v>109.9</v>
       </c>
       <c r="F19">
-        <v>282171</v>
+        <v>215142</v>
       </c>
       <c r="G19">
-        <v>102.5</v>
+        <v>100.6</v>
       </c>
       <c r="H19">
         <v>1.0347</v>
@@ -935,22 +935,22 @@
         <v>45504</v>
       </c>
       <c r="B20">
-        <v>25650230</v>
+        <v>26096585</v>
       </c>
       <c r="C20">
-        <v>10285725</v>
+        <v>9940840</v>
       </c>
       <c r="D20">
-        <v>5613492</v>
+        <v>8169061</v>
       </c>
       <c r="E20">
-        <v>186.4</v>
+        <v>216.7</v>
       </c>
       <c r="F20">
-        <v>260443</v>
+        <v>237661</v>
       </c>
       <c r="G20">
-        <v>102.9</v>
+        <v>122.1</v>
       </c>
       <c r="H20">
         <v>1.0266</v>
@@ -964,22 +964,22 @@
         <v>45535</v>
       </c>
       <c r="B21">
-        <v>24791769</v>
+        <v>24745080</v>
       </c>
       <c r="C21">
-        <v>7496764</v>
+        <v>7952474</v>
       </c>
       <c r="D21">
-        <v>4613556</v>
+        <v>3400941</v>
       </c>
       <c r="E21">
-        <v>143.4</v>
+        <v>190.9</v>
       </c>
       <c r="F21">
-        <v>476185</v>
+        <v>812838</v>
       </c>
       <c r="G21">
-        <v>84.09999999999999</v>
+        <v>125.3</v>
       </c>
       <c r="H21">
         <v>1.0804</v>
@@ -993,22 +993,22 @@
         <v>45565</v>
       </c>
       <c r="B22">
-        <v>26075810</v>
+        <v>26943174</v>
       </c>
       <c r="C22">
-        <v>7418975</v>
+        <v>9989004</v>
       </c>
       <c r="D22">
-        <v>4363375</v>
+        <v>3886089</v>
       </c>
       <c r="E22">
-        <v>214.1</v>
+        <v>230.7</v>
       </c>
       <c r="F22">
-        <v>426643</v>
+        <v>899764</v>
       </c>
       <c r="G22">
-        <v>63.4</v>
+        <v>33.9</v>
       </c>
       <c r="H22">
         <v>1.005</v>
@@ -1022,22 +1022,22 @@
         <v>45596</v>
       </c>
       <c r="B23">
-        <v>25769061</v>
+        <v>25512937</v>
       </c>
       <c r="C23">
-        <v>6020105</v>
+        <v>10200657</v>
       </c>
       <c r="D23">
-        <v>5866425</v>
+        <v>4896569</v>
       </c>
       <c r="E23">
-        <v>198.7</v>
+        <v>261.9</v>
       </c>
       <c r="F23">
-        <v>322351</v>
+        <v>391071</v>
       </c>
       <c r="G23">
-        <v>128.4</v>
+        <v>159.1</v>
       </c>
       <c r="H23">
         <v>0.9516</v>
@@ -1051,22 +1051,22 @@
         <v>45626</v>
       </c>
       <c r="B24">
-        <v>25738140</v>
+        <v>26354841</v>
       </c>
       <c r="C24">
-        <v>7974572</v>
+        <v>13508027</v>
       </c>
       <c r="D24">
-        <v>4715332</v>
+        <v>4566178</v>
       </c>
       <c r="E24">
-        <v>113.4</v>
+        <v>184.6</v>
       </c>
       <c r="F24">
-        <v>338228</v>
+        <v>401116</v>
       </c>
       <c r="G24">
-        <v>70.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H24">
         <v>1.0603</v>
@@ -1080,22 +1080,22 @@
         <v>45657</v>
       </c>
       <c r="B25">
-        <v>25281207</v>
+        <v>26255025</v>
       </c>
       <c r="C25">
-        <v>12958407</v>
+        <v>21422565</v>
       </c>
       <c r="D25">
-        <v>3201580</v>
+        <v>2069682</v>
       </c>
       <c r="E25">
-        <v>194.6</v>
+        <v>277</v>
       </c>
       <c r="F25">
-        <v>273980</v>
+        <v>632366</v>
       </c>
       <c r="G25">
-        <v>184.3</v>
+        <v>213.5</v>
       </c>
       <c r="H25">
         <v>0.999</v>
@@ -1109,22 +1109,22 @@
         <v>45688</v>
       </c>
       <c r="B26">
-        <v>24034044</v>
+        <v>25463979</v>
       </c>
       <c r="C26">
-        <v>8690307</v>
+        <v>8147501</v>
       </c>
       <c r="D26">
-        <v>3704040</v>
+        <v>4414584</v>
       </c>
       <c r="E26">
-        <v>101.4</v>
+        <v>148</v>
       </c>
       <c r="F26">
-        <v>376265</v>
+        <v>733838</v>
       </c>
       <c r="G26">
-        <v>215.8</v>
+        <v>269.9</v>
       </c>
       <c r="H26">
         <v>1.0166</v>
@@ -1138,22 +1138,22 @@
         <v>45716</v>
       </c>
       <c r="B27">
-        <v>27658136</v>
+        <v>27450256</v>
       </c>
       <c r="C27">
-        <v>7071812</v>
+        <v>5212420</v>
       </c>
       <c r="D27">
-        <v>7722716</v>
+        <v>8186626</v>
       </c>
       <c r="E27">
-        <v>112.9</v>
+        <v>66.7</v>
       </c>
       <c r="F27">
-        <v>772661</v>
+        <v>955426</v>
       </c>
       <c r="G27">
-        <v>95.3</v>
+        <v>59</v>
       </c>
       <c r="H27">
         <v>1.0532</v>
@@ -1167,22 +1167,22 @@
         <v>45747</v>
       </c>
       <c r="B28">
-        <v>28200170</v>
+        <v>26553244</v>
       </c>
       <c r="C28">
-        <v>10584394</v>
+        <v>8574192</v>
       </c>
       <c r="D28">
-        <v>6988196</v>
+        <v>4722335</v>
       </c>
       <c r="E28">
-        <v>108.1</v>
+        <v>114.6</v>
       </c>
       <c r="F28">
-        <v>553545</v>
+        <v>824655</v>
       </c>
       <c r="G28">
-        <v>91.2</v>
+        <v>89.5</v>
       </c>
       <c r="H28">
         <v>0.9664</v>
@@ -1196,22 +1196,22 @@
         <v>45777</v>
       </c>
       <c r="B29">
-        <v>26835580</v>
+        <v>25333269</v>
       </c>
       <c r="C29">
-        <v>7303026</v>
+        <v>5115513</v>
       </c>
       <c r="D29">
-        <v>6168547</v>
+        <v>5005127</v>
       </c>
       <c r="E29">
-        <v>239.6</v>
+        <v>198.7</v>
       </c>
       <c r="F29">
-        <v>420038</v>
+        <v>462790</v>
       </c>
       <c r="G29">
-        <v>147.4</v>
+        <v>141</v>
       </c>
       <c r="H29">
         <v>0.9775</v>
@@ -1225,22 +1225,22 @@
         <v>45808</v>
       </c>
       <c r="B30">
-        <v>24627269</v>
+        <v>25602939</v>
       </c>
       <c r="C30">
-        <v>8204439</v>
+        <v>6461711</v>
       </c>
       <c r="D30">
-        <v>4397215</v>
+        <v>5027419</v>
       </c>
       <c r="E30">
-        <v>94</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F30">
-        <v>282048</v>
+        <v>338697</v>
       </c>
       <c r="G30">
-        <v>165.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H30">
         <v>0.9675</v>
@@ -1254,22 +1254,22 @@
         <v>45838</v>
       </c>
       <c r="B31">
-        <v>27560807</v>
+        <v>25752833</v>
       </c>
       <c r="C31">
-        <v>12140944</v>
+        <v>12401565</v>
       </c>
       <c r="D31">
-        <v>8174674</v>
+        <v>11031499</v>
       </c>
       <c r="E31">
-        <v>75</v>
+        <v>69.5</v>
       </c>
       <c r="F31">
-        <v>627686</v>
+        <v>390508</v>
       </c>
       <c r="G31">
-        <v>173.9</v>
+        <v>199.2</v>
       </c>
       <c r="H31">
         <v>0.9923</v>
@@ -1283,22 +1283,22 @@
         <v>45869</v>
       </c>
       <c r="B32">
-        <v>27771314</v>
+        <v>26874629</v>
       </c>
       <c r="C32">
-        <v>9857170</v>
+        <v>9657800</v>
       </c>
       <c r="D32">
-        <v>7582003</v>
+        <v>12268484</v>
       </c>
       <c r="E32">
-        <v>161.8</v>
+        <v>189.2</v>
       </c>
       <c r="F32">
-        <v>870250</v>
+        <v>1045879</v>
       </c>
       <c r="G32">
-        <v>172.9</v>
+        <v>183.9</v>
       </c>
       <c r="H32">
         <v>1.0299</v>
@@ -1312,22 +1312,22 @@
         <v>45900</v>
       </c>
       <c r="B33">
-        <v>28680435</v>
+        <v>26242069</v>
       </c>
       <c r="C33">
-        <v>9544022</v>
+        <v>11062482</v>
       </c>
       <c r="D33">
-        <v>7543760</v>
+        <v>13683872</v>
       </c>
       <c r="E33">
-        <v>298.4</v>
+        <v>479</v>
       </c>
       <c r="F33">
-        <v>553878</v>
+        <v>507054</v>
       </c>
       <c r="G33">
-        <v>121</v>
+        <v>186.4</v>
       </c>
       <c r="H33">
         <v>1.0329</v>
@@ -1341,22 +1341,22 @@
         <v>45930</v>
       </c>
       <c r="B34">
-        <v>26602047</v>
+        <v>26817260</v>
       </c>
       <c r="C34">
-        <v>5851554</v>
+        <v>8597828</v>
       </c>
       <c r="D34">
-        <v>5355524</v>
+        <v>6404333</v>
       </c>
       <c r="E34">
-        <v>199</v>
+        <v>154.2</v>
       </c>
       <c r="F34">
-        <v>314803</v>
+        <v>466488</v>
       </c>
       <c r="G34">
-        <v>112.9</v>
+        <v>115.6</v>
       </c>
       <c r="H34">
         <v>1.0261</v>
@@ -1370,22 +1370,22 @@
         <v>45961</v>
       </c>
       <c r="B35">
-        <v>26245961</v>
+        <v>25805853</v>
       </c>
       <c r="C35">
-        <v>5213569</v>
+        <v>6941283</v>
       </c>
       <c r="D35">
-        <v>4145429</v>
+        <v>3257957</v>
       </c>
       <c r="E35">
-        <v>182.6</v>
+        <v>226.8</v>
       </c>
       <c r="F35">
-        <v>189077</v>
+        <v>174299</v>
       </c>
       <c r="G35">
-        <v>72.59999999999999</v>
+        <v>97</v>
       </c>
       <c r="H35">
         <v>0.976</v>
@@ -1399,22 +1399,22 @@
         <v>45991</v>
       </c>
       <c r="B36">
-        <v>25777450</v>
+        <v>25968449</v>
       </c>
       <c r="C36">
-        <v>5351401</v>
+        <v>7402834</v>
       </c>
       <c r="D36">
-        <v>3110770</v>
+        <v>1289586</v>
       </c>
       <c r="E36">
-        <v>180.4</v>
+        <v>218.8</v>
       </c>
       <c r="F36">
-        <v>317666</v>
+        <v>871709</v>
       </c>
       <c r="G36">
-        <v>149.2</v>
+        <v>201.3</v>
       </c>
       <c r="H36">
         <v>0.9496</v>
@@ -1428,22 +1428,22 @@
         <v>46022</v>
       </c>
       <c r="B37">
-        <v>28989709</v>
+        <v>28108338</v>
       </c>
       <c r="C37">
-        <v>5889815</v>
+        <v>5452793</v>
       </c>
       <c r="D37">
-        <v>7613578</v>
+        <v>9091501</v>
       </c>
       <c r="E37">
-        <v>177.8</v>
+        <v>231.3</v>
       </c>
       <c r="F37">
-        <v>785948</v>
+        <v>826529</v>
       </c>
       <c r="G37">
-        <v>61</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H37">
         <v>1.0211</v>

--- a/tools/synthetic_pilots/synth_fmcg_brand.xlsx
+++ b/tools/synthetic_pilots/synth_fmcg_brand.xlsx
@@ -437,31 +437,31 @@
         <v>44592</v>
       </c>
       <c r="B2">
-        <v>163659015</v>
+        <v>175384601</v>
       </c>
       <c r="C2">
-        <v>18588478</v>
+        <v>32393432</v>
       </c>
       <c r="D2">
-        <v>76.40000000000001</v>
+        <v>133.1</v>
       </c>
       <c r="E2">
-        <v>9633042</v>
+        <v>8331148</v>
       </c>
       <c r="F2">
-        <v>47526316</v>
+        <v>41103189</v>
       </c>
       <c r="G2">
-        <v>18124</v>
+        <v>17226</v>
       </c>
       <c r="H2">
-        <v>224400</v>
+        <v>213283</v>
       </c>
       <c r="I2">
-        <v>25389</v>
+        <v>8240</v>
       </c>
       <c r="J2">
-        <v>565</v>
+        <v>183</v>
       </c>
       <c r="K2">
         <v>188.2</v>
@@ -470,7 +470,7 @@
         <v>1.0255</v>
       </c>
       <c r="M2">
-        <v>1035656272</v>
+        <v>1062650202</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -478,31 +478,31 @@
         <v>44620</v>
       </c>
       <c r="B3">
-        <v>175191361</v>
+        <v>173654637</v>
       </c>
       <c r="C3">
-        <v>169297</v>
+        <v>299907</v>
       </c>
       <c r="D3">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E3">
-        <v>7261038</v>
+        <v>6145828</v>
       </c>
       <c r="F3">
-        <v>38080180</v>
+        <v>32231515</v>
       </c>
       <c r="G3">
-        <v>4505607</v>
+        <v>4358034</v>
       </c>
       <c r="H3">
-        <v>57587785</v>
+        <v>55701606</v>
       </c>
       <c r="I3">
-        <v>2441055</v>
+        <v>806709</v>
       </c>
       <c r="J3">
-        <v>52372</v>
+        <v>17308</v>
       </c>
       <c r="K3">
         <v>102.3</v>
@@ -511,7 +511,7 @@
         <v>0.9792</v>
       </c>
       <c r="M3">
-        <v>930904336</v>
+        <v>955167952</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -519,31 +519,31 @@
         <v>44651</v>
       </c>
       <c r="B4">
-        <v>165647032</v>
+        <v>153808915</v>
       </c>
       <c r="C4">
-        <v>284283</v>
+        <v>494006</v>
       </c>
       <c r="D4">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="E4">
-        <v>4763458</v>
+        <v>4064009</v>
       </c>
       <c r="F4">
-        <v>23245248</v>
+        <v>19832000</v>
       </c>
       <c r="G4">
-        <v>1223166</v>
+        <v>1165372</v>
       </c>
       <c r="H4">
-        <v>15082943</v>
+        <v>14370281</v>
       </c>
       <c r="I4">
-        <v>6549821</v>
+        <v>2175698</v>
       </c>
       <c r="J4">
-        <v>148702</v>
+        <v>49396</v>
       </c>
       <c r="K4">
         <v>115.4</v>
@@ -552,7 +552,7 @@
         <v>1.0299</v>
       </c>
       <c r="M4">
-        <v>873658577</v>
+        <v>896430107</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -560,31 +560,31 @@
         <v>44681</v>
       </c>
       <c r="B5">
-        <v>158043681</v>
+        <v>153106048</v>
       </c>
       <c r="C5">
-        <v>10617912</v>
+        <v>18557555</v>
       </c>
       <c r="D5">
-        <v>41.9</v>
+        <v>73.2</v>
       </c>
       <c r="E5">
-        <v>5133326</v>
+        <v>4455814</v>
       </c>
       <c r="F5">
-        <v>26161533</v>
+        <v>22708653</v>
       </c>
       <c r="G5">
-        <v>78372</v>
+        <v>75758</v>
       </c>
       <c r="H5">
-        <v>933591</v>
+        <v>902452</v>
       </c>
       <c r="I5">
-        <v>3957227</v>
+        <v>1311676</v>
       </c>
       <c r="J5">
-        <v>89292</v>
+        <v>29597</v>
       </c>
       <c r="K5">
         <v>216.4</v>
@@ -593,7 +593,7 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="M5">
-        <v>869027034</v>
+        <v>891677845</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -601,31 +601,31 @@
         <v>44712</v>
       </c>
       <c r="B6">
-        <v>158232583</v>
+        <v>155618881</v>
       </c>
       <c r="C6">
-        <v>5205011</v>
+        <v>9569794</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>38.5</v>
       </c>
       <c r="E6">
-        <v>8970918</v>
+        <v>7735884</v>
       </c>
       <c r="F6">
-        <v>43810045</v>
+        <v>37778678</v>
       </c>
       <c r="G6">
-        <v>9136345</v>
+        <v>8835669</v>
       </c>
       <c r="H6">
-        <v>113433982</v>
+        <v>109700886</v>
       </c>
       <c r="I6">
-        <v>2586062</v>
+        <v>860423</v>
       </c>
       <c r="J6">
-        <v>55594</v>
+        <v>18497</v>
       </c>
       <c r="K6">
         <v>101.2</v>
@@ -634,7 +634,7 @@
         <v>0.987</v>
       </c>
       <c r="M6">
-        <v>764813379</v>
+        <v>784747906</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -642,31 +642,31 @@
         <v>44742</v>
       </c>
       <c r="B7">
-        <v>146152561</v>
+        <v>152372661</v>
       </c>
       <c r="C7">
-        <v>15452300</v>
+        <v>26761370</v>
       </c>
       <c r="D7">
-        <v>60.2</v>
+        <v>104.2</v>
       </c>
       <c r="E7">
-        <v>1736373</v>
+        <v>1398691</v>
       </c>
       <c r="F7">
-        <v>9065451</v>
+        <v>7302442</v>
       </c>
       <c r="G7">
-        <v>7467618</v>
+        <v>7225761</v>
       </c>
       <c r="H7">
-        <v>98295732</v>
+        <v>95112184</v>
       </c>
       <c r="I7">
-        <v>1743752</v>
+        <v>567257</v>
       </c>
       <c r="J7">
-        <v>38993</v>
+        <v>12685</v>
       </c>
       <c r="K7">
         <v>228.9</v>
@@ -675,7 +675,7 @@
         <v>1.0293</v>
       </c>
       <c r="M7">
-        <v>814732897</v>
+        <v>835968555</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -683,31 +683,31 @@
         <v>44773</v>
       </c>
       <c r="B8">
-        <v>155075556</v>
+        <v>158295167</v>
       </c>
       <c r="C8">
-        <v>6595343</v>
+        <v>11498782</v>
       </c>
       <c r="D8">
-        <v>25.7</v>
+        <v>44.8</v>
       </c>
       <c r="E8">
-        <v>5346421</v>
+        <v>4721253</v>
       </c>
       <c r="F8">
-        <v>26260729</v>
+        <v>23190006</v>
       </c>
       <c r="G8">
-        <v>91670</v>
+        <v>88582</v>
       </c>
       <c r="H8">
-        <v>1141344</v>
+        <v>1102891</v>
       </c>
       <c r="I8">
-        <v>2915679</v>
+        <v>968348</v>
       </c>
       <c r="J8">
-        <v>63274</v>
+        <v>21014</v>
       </c>
       <c r="K8">
         <v>110</v>
@@ -716,7 +716,7 @@
         <v>1.0034</v>
       </c>
       <c r="M8">
-        <v>822260383</v>
+        <v>843692241</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -724,31 +724,31 @@
         <v>44804</v>
       </c>
       <c r="B9">
-        <v>163898292</v>
+        <v>170744566</v>
       </c>
       <c r="C9">
-        <v>10121156</v>
+        <v>17630185</v>
       </c>
       <c r="D9">
-        <v>40.3</v>
+        <v>70.3</v>
       </c>
       <c r="E9">
-        <v>10259887</v>
+        <v>9085985</v>
       </c>
       <c r="F9">
-        <v>52124162</v>
+        <v>46160290</v>
       </c>
       <c r="G9">
-        <v>3873090</v>
+        <v>3741856</v>
       </c>
       <c r="H9">
-        <v>49337307</v>
+        <v>47665587</v>
       </c>
       <c r="I9">
-        <v>1548443</v>
+        <v>505055</v>
       </c>
       <c r="J9">
-        <v>34131</v>
+        <v>11132</v>
       </c>
       <c r="K9">
         <v>199.7</v>
@@ -757,7 +757,7 @@
         <v>1.0113</v>
       </c>
       <c r="M9">
-        <v>856078283</v>
+        <v>878391590</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -765,31 +765,31 @@
         <v>44834</v>
       </c>
       <c r="B10">
-        <v>176692278</v>
+        <v>180533086</v>
       </c>
       <c r="C10">
-        <v>4532930</v>
+        <v>8287936</v>
       </c>
       <c r="D10">
-        <v>17.9</v>
+        <v>32.7</v>
       </c>
       <c r="E10">
-        <v>3244471</v>
+        <v>2690339</v>
       </c>
       <c r="F10">
-        <v>16327313</v>
+        <v>13538726</v>
       </c>
       <c r="G10">
-        <v>3852412</v>
+        <v>3716706</v>
       </c>
       <c r="H10">
-        <v>47085338</v>
+        <v>45426701</v>
       </c>
       <c r="I10">
-        <v>2678140</v>
+        <v>877431</v>
       </c>
       <c r="J10">
-        <v>56407</v>
+        <v>18480</v>
       </c>
       <c r="K10">
         <v>86.09999999999999</v>
@@ -798,7 +798,7 @@
         <v>1.0038</v>
       </c>
       <c r="M10">
-        <v>976720882</v>
+        <v>1002178686</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -806,31 +806,31 @@
         <v>44865</v>
       </c>
       <c r="B11">
-        <v>192642789</v>
+        <v>192114122</v>
       </c>
       <c r="C11">
-        <v>6973682</v>
+        <v>12344405</v>
       </c>
       <c r="D11">
-        <v>26.5</v>
+        <v>46.8</v>
       </c>
       <c r="E11">
-        <v>6688840</v>
+        <v>5819856</v>
       </c>
       <c r="F11">
-        <v>31559540</v>
+        <v>27459463</v>
       </c>
       <c r="G11">
-        <v>2760213</v>
+        <v>2666676</v>
       </c>
       <c r="H11">
-        <v>33337173</v>
+        <v>32207453</v>
       </c>
       <c r="I11">
-        <v>4820074</v>
+        <v>1600140</v>
       </c>
       <c r="J11">
-        <v>106550</v>
+        <v>35372</v>
       </c>
       <c r="K11">
         <v>60.8</v>
@@ -839,7 +839,7 @@
         <v>1.0138</v>
       </c>
       <c r="M11">
-        <v>951576438</v>
+        <v>976378863</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -847,31 +847,31 @@
         <v>44895</v>
       </c>
       <c r="B12">
-        <v>177579677</v>
+        <v>190037330</v>
       </c>
       <c r="C12">
-        <v>9931418</v>
+        <v>17680342</v>
       </c>
       <c r="D12">
-        <v>37.9</v>
+        <v>67.5</v>
       </c>
       <c r="E12">
-        <v>3593224</v>
+        <v>2960055</v>
       </c>
       <c r="F12">
-        <v>17123344</v>
+        <v>14106004</v>
       </c>
       <c r="G12">
-        <v>1565201</v>
+        <v>1493555</v>
       </c>
       <c r="H12">
-        <v>19795331</v>
+        <v>18889212</v>
       </c>
       <c r="I12">
-        <v>74113</v>
+        <v>24699</v>
       </c>
       <c r="J12">
-        <v>1582</v>
+        <v>527</v>
       </c>
       <c r="K12">
         <v>106.5</v>
@@ -880,7 +880,7 @@
         <v>1.0169</v>
       </c>
       <c r="M12">
-        <v>1102745680</v>
+        <v>1131488265</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -888,31 +888,31 @@
         <v>44926</v>
       </c>
       <c r="B13">
-        <v>210691375</v>
+        <v>217960685</v>
       </c>
       <c r="C13">
-        <v>24518970</v>
+        <v>42520624</v>
       </c>
       <c r="D13">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E13">
-        <v>8146528</v>
+        <v>7140124</v>
       </c>
       <c r="F13">
-        <v>39678393</v>
+        <v>34776610</v>
       </c>
       <c r="G13">
-        <v>3661089</v>
+        <v>3527354</v>
       </c>
       <c r="H13">
-        <v>45987012</v>
+        <v>44307163</v>
       </c>
       <c r="I13">
-        <v>4058899</v>
+        <v>1344849</v>
       </c>
       <c r="J13">
-        <v>86793</v>
+        <v>28758</v>
       </c>
       <c r="K13">
         <v>79.2</v>
@@ -921,7 +921,7 @@
         <v>0.9465</v>
       </c>
       <c r="M13">
-        <v>1026800507</v>
+        <v>1053563614</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -929,31 +929,31 @@
         <v>44957</v>
       </c>
       <c r="B14">
-        <v>193831181</v>
+        <v>204658751</v>
       </c>
       <c r="C14">
-        <v>217709</v>
+        <v>381371</v>
       </c>
       <c r="D14">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E14">
-        <v>7883022</v>
+        <v>6684788</v>
       </c>
       <c r="F14">
-        <v>35972139</v>
+        <v>30504310</v>
       </c>
       <c r="G14">
-        <v>4717543</v>
+        <v>4543786</v>
       </c>
       <c r="H14">
-        <v>55360596</v>
+        <v>53321553</v>
       </c>
       <c r="I14">
-        <v>824599</v>
+        <v>265761</v>
       </c>
       <c r="J14">
-        <v>18113</v>
+        <v>5838</v>
       </c>
       <c r="K14">
         <v>36.3</v>
@@ -962,7 +962,7 @@
         <v>1.025</v>
       </c>
       <c r="M14">
-        <v>971461188</v>
+        <v>996781901</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -970,31 +970,31 @@
         <v>44985</v>
       </c>
       <c r="B15">
-        <v>183449021</v>
+        <v>201122730</v>
       </c>
       <c r="C15">
-        <v>15402299</v>
+        <v>26795918</v>
       </c>
       <c r="D15">
-        <v>58</v>
+        <v>100.9</v>
       </c>
       <c r="E15">
-        <v>7485498</v>
+        <v>6556049</v>
       </c>
       <c r="F15">
-        <v>35979978</v>
+        <v>31512468</v>
       </c>
       <c r="G15">
-        <v>5485364</v>
+        <v>5303004</v>
       </c>
       <c r="H15">
-        <v>66080076</v>
+        <v>63883259</v>
       </c>
       <c r="I15">
-        <v>58950</v>
+        <v>19534</v>
       </c>
       <c r="J15">
-        <v>1304</v>
+        <v>432</v>
       </c>
       <c r="K15">
         <v>46.9</v>
@@ -1003,7 +1003,7 @@
         <v>0.976</v>
       </c>
       <c r="M15">
-        <v>988163908</v>
+        <v>1013919969</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1011,31 +1011,31 @@
         <v>45016</v>
       </c>
       <c r="B16">
-        <v>186316457</v>
+        <v>191597036</v>
       </c>
       <c r="C16">
-        <v>4351252</v>
+        <v>7705869</v>
       </c>
       <c r="D16">
-        <v>16.9</v>
+        <v>29.9</v>
       </c>
       <c r="E16">
-        <v>9707291</v>
+        <v>8532709</v>
       </c>
       <c r="F16">
-        <v>45817086</v>
+        <v>40273220</v>
       </c>
       <c r="G16">
-        <v>950391</v>
+        <v>914653</v>
       </c>
       <c r="H16">
-        <v>12160768</v>
+        <v>11703478</v>
       </c>
       <c r="I16">
-        <v>3087766</v>
+        <v>993739</v>
       </c>
       <c r="J16">
-        <v>63528</v>
+        <v>20445</v>
       </c>
       <c r="K16">
         <v>95.40000000000001</v>
@@ -1044,7 +1044,7 @@
         <v>0.9626</v>
       </c>
       <c r="M16">
-        <v>891763748</v>
+        <v>915007181</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1052,31 +1052,31 @@
         <v>45046</v>
       </c>
       <c r="B17">
-        <v>159800148</v>
+        <v>159346250</v>
       </c>
       <c r="C17">
-        <v>117077</v>
+        <v>211268</v>
       </c>
       <c r="D17">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E17">
-        <v>36025</v>
+        <v>31730</v>
       </c>
       <c r="F17">
-        <v>168173</v>
+        <v>148124</v>
       </c>
       <c r="G17">
-        <v>67523</v>
+        <v>64893</v>
       </c>
       <c r="H17">
-        <v>776115</v>
+        <v>745883</v>
       </c>
       <c r="I17">
-        <v>4180071</v>
+        <v>1391400</v>
       </c>
       <c r="J17">
-        <v>88357</v>
+        <v>29411</v>
       </c>
       <c r="K17">
         <v>27.4</v>
@@ -1085,7 +1085,7 @@
         <v>1.0045</v>
       </c>
       <c r="M17">
-        <v>851679858</v>
+        <v>873878522</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1093,31 +1093,31 @@
         <v>45077</v>
       </c>
       <c r="B18">
-        <v>159893209</v>
+        <v>159227342</v>
       </c>
       <c r="C18">
-        <v>9590079</v>
+        <v>16872298</v>
       </c>
       <c r="D18">
-        <v>37.6</v>
+        <v>66.2</v>
       </c>
       <c r="E18">
-        <v>3746567</v>
+        <v>3085813</v>
       </c>
       <c r="F18">
-        <v>17894695</v>
+        <v>14738742</v>
       </c>
       <c r="G18">
-        <v>5517422</v>
+        <v>5322886</v>
       </c>
       <c r="H18">
-        <v>64133256</v>
+        <v>61872013</v>
       </c>
       <c r="I18">
-        <v>4826873</v>
+        <v>1602388</v>
       </c>
       <c r="J18">
-        <v>103741</v>
+        <v>34439</v>
       </c>
       <c r="K18">
         <v>63.2</v>
@@ -1126,7 +1126,7 @@
         <v>1.0092</v>
       </c>
       <c r="M18">
-        <v>852396692</v>
+        <v>874614040</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1134,31 +1134,31 @@
         <v>45107</v>
       </c>
       <c r="B19">
-        <v>153050024</v>
+        <v>156389867</v>
       </c>
       <c r="C19">
-        <v>5812366</v>
+        <v>10746145</v>
       </c>
       <c r="D19">
-        <v>21.3</v>
+        <v>39.4</v>
       </c>
       <c r="E19">
-        <v>6144652</v>
+        <v>5445714</v>
       </c>
       <c r="F19">
-        <v>28868481</v>
+        <v>25584771</v>
       </c>
       <c r="G19">
-        <v>3797527</v>
+        <v>3639623</v>
       </c>
       <c r="H19">
-        <v>46223722</v>
+        <v>44301705</v>
       </c>
       <c r="I19">
-        <v>1757072</v>
+        <v>572332</v>
       </c>
       <c r="J19">
-        <v>37315</v>
+        <v>12155</v>
       </c>
       <c r="K19">
         <v>136</v>
@@ -1167,7 +1167,7 @@
         <v>0.9863</v>
       </c>
       <c r="M19">
-        <v>844354135</v>
+        <v>866361857</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1175,31 +1175,31 @@
         <v>45138</v>
       </c>
       <c r="B20">
-        <v>136800712</v>
+        <v>138471764</v>
       </c>
       <c r="C20">
-        <v>300091</v>
+        <v>521995</v>
       </c>
       <c r="D20">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="E20">
-        <v>2438278</v>
+        <v>2053118</v>
       </c>
       <c r="F20">
-        <v>11760484</v>
+        <v>9902750</v>
       </c>
       <c r="G20">
-        <v>4058394</v>
+        <v>3873443</v>
       </c>
       <c r="H20">
-        <v>50134252</v>
+        <v>47849512</v>
       </c>
       <c r="I20">
-        <v>1799521</v>
+        <v>582244</v>
       </c>
       <c r="J20">
-        <v>36716</v>
+        <v>11880</v>
       </c>
       <c r="K20">
         <v>160.7</v>
@@ -1208,7 +1208,7 @@
         <v>1.0324</v>
       </c>
       <c r="M20">
-        <v>822123010</v>
+        <v>843551287</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1216,31 +1216,31 @@
         <v>45169</v>
       </c>
       <c r="B21">
-        <v>145215679</v>
+        <v>152128924</v>
       </c>
       <c r="C21">
-        <v>12423122</v>
+        <v>21774137</v>
       </c>
       <c r="D21">
-        <v>47.3</v>
+        <v>83</v>
       </c>
       <c r="E21">
-        <v>2244131</v>
+        <v>1816135</v>
       </c>
       <c r="F21">
-        <v>10742373</v>
+        <v>8693611</v>
       </c>
       <c r="G21">
-        <v>1764345</v>
+        <v>1698414</v>
       </c>
       <c r="H21">
-        <v>20343408</v>
+        <v>19583205</v>
       </c>
       <c r="I21">
-        <v>1607525</v>
+        <v>523995</v>
       </c>
       <c r="J21">
-        <v>36259</v>
+        <v>11819</v>
       </c>
       <c r="K21">
         <v>209.3</v>
@@ -1249,7 +1249,7 @@
         <v>0.9677</v>
       </c>
       <c r="M21">
-        <v>921562774</v>
+        <v>945582906</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1257,31 +1257,31 @@
         <v>45199</v>
       </c>
       <c r="B22">
-        <v>158518417</v>
+        <v>173237077</v>
       </c>
       <c r="C22">
-        <v>10695214</v>
+        <v>18648866</v>
       </c>
       <c r="D22">
-        <v>39.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E22">
-        <v>6230690</v>
+        <v>5421531</v>
       </c>
       <c r="F22">
-        <v>27627633</v>
+        <v>24039725</v>
       </c>
       <c r="G22">
-        <v>53207</v>
+        <v>51166</v>
       </c>
       <c r="H22">
-        <v>607561</v>
+        <v>584249</v>
       </c>
       <c r="I22">
-        <v>97621</v>
+        <v>32533</v>
       </c>
       <c r="J22">
-        <v>2097</v>
+        <v>699</v>
       </c>
       <c r="K22">
         <v>57.1</v>
@@ -1290,7 +1290,7 @@
         <v>0.9961</v>
       </c>
       <c r="M22">
-        <v>989158262</v>
+        <v>1014940241</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1298,31 +1298,31 @@
         <v>45230</v>
       </c>
       <c r="B23">
-        <v>181548692</v>
+        <v>187224020</v>
       </c>
       <c r="C23">
-        <v>6315396</v>
+        <v>11257551</v>
       </c>
       <c r="D23">
-        <v>25</v>
+        <v>44.6</v>
       </c>
       <c r="E23">
-        <v>7421469</v>
+        <v>6358612</v>
       </c>
       <c r="F23">
-        <v>35221220</v>
+        <v>30177053</v>
       </c>
       <c r="G23">
-        <v>3182621</v>
+        <v>3047354</v>
       </c>
       <c r="H23">
-        <v>34141482</v>
+        <v>32690412</v>
       </c>
       <c r="I23">
-        <v>2446687</v>
+        <v>807505</v>
       </c>
       <c r="J23">
-        <v>51420</v>
+        <v>16971</v>
       </c>
       <c r="K23">
         <v>156.9</v>
@@ -1331,7 +1331,7 @@
         <v>0.9912</v>
       </c>
       <c r="M23">
-        <v>1062206100</v>
+        <v>1089892039</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1339,31 +1339,31 @@
         <v>45260</v>
       </c>
       <c r="B24">
-        <v>194571776</v>
+        <v>201189982</v>
       </c>
       <c r="C24">
-        <v>23304014</v>
+        <v>40364803</v>
       </c>
       <c r="D24">
-        <v>88.5</v>
+        <v>153.2</v>
       </c>
       <c r="E24">
-        <v>4007272</v>
+        <v>3539223</v>
       </c>
       <c r="F24">
-        <v>19786105</v>
+        <v>17475090</v>
       </c>
       <c r="G24">
-        <v>1617439</v>
+        <v>1553885</v>
       </c>
       <c r="H24">
-        <v>18289735</v>
+        <v>17571078</v>
       </c>
       <c r="I24">
-        <v>4431758</v>
+        <v>1473054</v>
       </c>
       <c r="J24">
-        <v>86425</v>
+        <v>28727</v>
       </c>
       <c r="K24">
         <v>183.7</v>
@@ -1372,7 +1372,7 @@
         <v>1.0078</v>
       </c>
       <c r="M24">
-        <v>1070809505</v>
+        <v>1098719688</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1380,31 +1380,31 @@
         <v>45291</v>
       </c>
       <c r="B25">
-        <v>208880637</v>
+        <v>218714701</v>
       </c>
       <c r="C25">
-        <v>17325120</v>
+        <v>30074527</v>
       </c>
       <c r="D25">
-        <v>63.8</v>
+        <v>110.8</v>
       </c>
       <c r="E25">
-        <v>9122423</v>
+        <v>8049395</v>
       </c>
       <c r="F25">
-        <v>39704384</v>
+        <v>35034145</v>
       </c>
       <c r="G25">
-        <v>4447070</v>
+        <v>4272233</v>
       </c>
       <c r="H25">
-        <v>50143803</v>
+        <v>48172393</v>
       </c>
       <c r="I25">
-        <v>2401100</v>
+        <v>795982</v>
       </c>
       <c r="J25">
-        <v>48282</v>
+        <v>16006</v>
       </c>
       <c r="K25">
         <v>34.7</v>
@@ -1413,7 +1413,7 @@
         <v>1.0179</v>
       </c>
       <c r="M25">
-        <v>1124554252</v>
+        <v>1153865268</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1421,31 +1421,31 @@
         <v>45322</v>
       </c>
       <c r="B26">
-        <v>201072369</v>
+        <v>208503440</v>
       </c>
       <c r="C26">
-        <v>10544149</v>
+        <v>18371984</v>
       </c>
       <c r="D26">
-        <v>39.6</v>
+        <v>69</v>
       </c>
       <c r="E26">
-        <v>4737445</v>
+        <v>4035109</v>
       </c>
       <c r="F26">
-        <v>20003943</v>
+        <v>17038315</v>
       </c>
       <c r="G26">
-        <v>64335</v>
+        <v>61754</v>
       </c>
       <c r="H26">
-        <v>734763</v>
+        <v>705279</v>
       </c>
       <c r="I26">
-        <v>3821058</v>
+        <v>1264931</v>
       </c>
       <c r="J26">
-        <v>75456</v>
+        <v>24979</v>
       </c>
       <c r="K26">
         <v>22.2</v>
@@ -1454,7 +1454,7 @@
         <v>0.9798</v>
       </c>
       <c r="M26">
-        <v>974311029</v>
+        <v>999706021</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1462,31 +1462,31 @@
         <v>45351</v>
       </c>
       <c r="B27">
-        <v>191069473</v>
+        <v>198327020</v>
       </c>
       <c r="C27">
-        <v>4428543</v>
+        <v>8022527</v>
       </c>
       <c r="D27">
-        <v>15.7</v>
+        <v>28.5</v>
       </c>
       <c r="E27">
-        <v>8324482</v>
+        <v>7387545</v>
       </c>
       <c r="F27">
-        <v>38159715</v>
+        <v>33864766</v>
       </c>
       <c r="G27">
-        <v>4007838</v>
+        <v>3851294</v>
       </c>
       <c r="H27">
-        <v>44286586</v>
+        <v>42556772</v>
       </c>
       <c r="I27">
-        <v>2226253</v>
+        <v>723661</v>
       </c>
       <c r="J27">
-        <v>46392</v>
+        <v>15080</v>
       </c>
       <c r="K27">
         <v>88.5</v>
@@ -1495,7 +1495,7 @@
         <v>1.0321</v>
       </c>
       <c r="M27">
-        <v>1001144849</v>
+        <v>1027239253</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1503,31 +1503,31 @@
         <v>45382</v>
       </c>
       <c r="B28">
-        <v>147479769</v>
+        <v>161062794</v>
       </c>
       <c r="C28">
-        <v>143067</v>
+        <v>252984</v>
       </c>
       <c r="D28">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E28">
-        <v>136834</v>
+        <v>116178</v>
       </c>
       <c r="F28">
-        <v>655377</v>
+        <v>556444</v>
       </c>
       <c r="G28">
-        <v>72592</v>
+        <v>70068</v>
       </c>
       <c r="H28">
-        <v>803639</v>
+        <v>775699</v>
       </c>
       <c r="I28">
-        <v>116446</v>
+        <v>38791</v>
       </c>
       <c r="J28">
-        <v>2416</v>
+        <v>805</v>
       </c>
       <c r="K28">
         <v>74.90000000000001</v>
@@ -1536,7 +1536,7 @@
         <v>1.0127</v>
       </c>
       <c r="M28">
-        <v>925637514</v>
+        <v>949763852</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1544,31 +1544,31 @@
         <v>45412</v>
       </c>
       <c r="B29">
-        <v>136796748</v>
+        <v>144988599</v>
       </c>
       <c r="C29">
-        <v>5372520</v>
+        <v>9973058</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>37.2</v>
       </c>
       <c r="E29">
-        <v>161699</v>
+        <v>140299</v>
       </c>
       <c r="F29">
-        <v>733572</v>
+        <v>636488</v>
       </c>
       <c r="G29">
-        <v>72988</v>
+        <v>70008</v>
       </c>
       <c r="H29">
-        <v>790412</v>
+        <v>758143</v>
       </c>
       <c r="I29">
-        <v>2054927</v>
+        <v>674242</v>
       </c>
       <c r="J29">
-        <v>40503</v>
+        <v>13289</v>
       </c>
       <c r="K29">
         <v>117.2</v>
@@ -1577,7 +1577,7 @@
         <v>0.9545</v>
       </c>
       <c r="M29">
-        <v>907783133</v>
+        <v>931444105</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1585,31 +1585,31 @@
         <v>45443</v>
       </c>
       <c r="B30">
-        <v>143360953</v>
+        <v>139781536</v>
       </c>
       <c r="C30">
-        <v>122001</v>
+        <v>222202</v>
       </c>
       <c r="D30">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E30">
-        <v>7573445</v>
+        <v>6400666</v>
       </c>
       <c r="F30">
-        <v>34204652</v>
+        <v>28907920</v>
       </c>
       <c r="G30">
-        <v>187496</v>
+        <v>181385</v>
       </c>
       <c r="H30">
-        <v>2132178</v>
+        <v>2062692</v>
       </c>
       <c r="I30">
-        <v>3607249</v>
+        <v>1194307</v>
       </c>
       <c r="J30">
-        <v>71661</v>
+        <v>23726</v>
       </c>
       <c r="K30">
         <v>192.1</v>
@@ -1618,7 +1618,7 @@
         <v>0.9529</v>
       </c>
       <c r="M30">
-        <v>843542384</v>
+        <v>865528949</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1626,31 +1626,31 @@
         <v>45473</v>
       </c>
       <c r="B31">
-        <v>145576125</v>
+        <v>148421684</v>
       </c>
       <c r="C31">
-        <v>13395014</v>
+        <v>23425056</v>
       </c>
       <c r="D31">
-        <v>48.4</v>
+        <v>84.7</v>
       </c>
       <c r="E31">
-        <v>177156</v>
+        <v>157122</v>
       </c>
       <c r="F31">
-        <v>811038</v>
+        <v>719317</v>
       </c>
       <c r="G31">
-        <v>7315498</v>
+        <v>7075458</v>
       </c>
       <c r="H31">
-        <v>84352313</v>
+        <v>81584502</v>
       </c>
       <c r="I31">
-        <v>3191562</v>
+        <v>1059323</v>
       </c>
       <c r="J31">
-        <v>63523</v>
+        <v>21084</v>
       </c>
       <c r="K31">
         <v>41.1</v>
@@ -1659,7 +1659,7 @@
         <v>1.0117</v>
       </c>
       <c r="M31">
-        <v>844119651</v>
+        <v>866121261</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1667,31 +1667,31 @@
         <v>45504</v>
       </c>
       <c r="B32">
-        <v>156932453</v>
+        <v>158830871</v>
       </c>
       <c r="C32">
-        <v>10890373</v>
+        <v>18998555</v>
       </c>
       <c r="D32">
-        <v>37.7</v>
+        <v>65.8</v>
       </c>
       <c r="E32">
-        <v>3125710</v>
+        <v>2603790</v>
       </c>
       <c r="F32">
-        <v>14665405</v>
+        <v>12216628</v>
       </c>
       <c r="G32">
-        <v>99683</v>
+        <v>95963</v>
       </c>
       <c r="H32">
-        <v>1146674</v>
+        <v>1103877</v>
       </c>
       <c r="I32">
-        <v>4307684</v>
+        <v>1428400</v>
       </c>
       <c r="J32">
-        <v>87318</v>
+        <v>28954</v>
       </c>
       <c r="K32">
         <v>8.300000000000001</v>
@@ -1700,7 +1700,7 @@
         <v>1.0059</v>
       </c>
       <c r="M32">
-        <v>932606191</v>
+        <v>956914165</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -1708,31 +1708,31 @@
         <v>45535</v>
       </c>
       <c r="B33">
-        <v>139939096</v>
+        <v>141698908</v>
       </c>
       <c r="C33">
-        <v>282953</v>
+        <v>490144</v>
       </c>
       <c r="D33">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="E33">
-        <v>3367723</v>
+        <v>2731187</v>
       </c>
       <c r="F33">
-        <v>14956712</v>
+        <v>12129730</v>
       </c>
       <c r="G33">
-        <v>4380685</v>
+        <v>4204984</v>
       </c>
       <c r="H33">
-        <v>48337593</v>
+        <v>46398864</v>
       </c>
       <c r="I33">
-        <v>1790406</v>
+        <v>596390</v>
       </c>
       <c r="J33">
-        <v>35657</v>
+        <v>11878</v>
       </c>
       <c r="K33">
         <v>276.1</v>
@@ -1741,7 +1741,7 @@
         <v>1.0098</v>
       </c>
       <c r="M33">
-        <v>905746937</v>
+        <v>929354836</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -1749,31 +1749,31 @@
         <v>45565</v>
       </c>
       <c r="B34">
-        <v>155329223</v>
+        <v>153963767</v>
       </c>
       <c r="C34">
-        <v>186039</v>
+        <v>332429</v>
       </c>
       <c r="D34">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E34">
-        <v>7053878</v>
+        <v>6080721</v>
       </c>
       <c r="F34">
-        <v>30637953</v>
+        <v>26411126</v>
       </c>
       <c r="G34">
-        <v>2950217</v>
+        <v>2842424</v>
       </c>
       <c r="H34">
-        <v>31139408</v>
+        <v>30001657</v>
       </c>
       <c r="I34">
-        <v>1980979</v>
+        <v>644097</v>
       </c>
       <c r="J34">
-        <v>38659</v>
+        <v>12570</v>
       </c>
       <c r="K34">
         <v>186</v>
@@ -1782,7 +1782,7 @@
         <v>1.0125</v>
       </c>
       <c r="M34">
-        <v>988492442</v>
+        <v>1014257067</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -1790,31 +1790,31 @@
         <v>45596</v>
       </c>
       <c r="B35">
-        <v>169119343</v>
+        <v>177495093</v>
       </c>
       <c r="C35">
-        <v>8036319</v>
+        <v>14306983</v>
       </c>
       <c r="D35">
-        <v>26.8</v>
+        <v>47.7</v>
       </c>
       <c r="E35">
-        <v>10381610</v>
+        <v>9225741</v>
       </c>
       <c r="F35">
-        <v>47775324</v>
+        <v>42456107</v>
       </c>
       <c r="G35">
-        <v>95190</v>
+        <v>92019</v>
       </c>
       <c r="H35">
-        <v>1060646</v>
+        <v>1025311</v>
       </c>
       <c r="I35">
-        <v>27587</v>
+        <v>9118</v>
       </c>
       <c r="J35">
-        <v>527</v>
+        <v>174</v>
       </c>
       <c r="K35">
         <v>35.3</v>
@@ -1823,7 +1823,7 @@
         <v>1.0205</v>
       </c>
       <c r="M35">
-        <v>1023528895</v>
+        <v>1050206730</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -1831,31 +1831,31 @@
         <v>45626</v>
       </c>
       <c r="B36">
-        <v>164394851</v>
+        <v>166606591</v>
       </c>
       <c r="C36">
-        <v>281893</v>
+        <v>498378</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E36">
-        <v>5722319</v>
+        <v>5066710</v>
       </c>
       <c r="F36">
-        <v>24546370</v>
+        <v>21734080</v>
       </c>
       <c r="G36">
-        <v>80986</v>
+        <v>78142</v>
       </c>
       <c r="H36">
-        <v>898158</v>
+        <v>866618</v>
       </c>
       <c r="I36">
-        <v>1406889</v>
+        <v>463511</v>
       </c>
       <c r="J36">
-        <v>26737</v>
+        <v>8809</v>
       </c>
       <c r="K36">
         <v>163.1</v>
@@ -1864,7 +1864,7 @@
         <v>1.0426</v>
       </c>
       <c r="M36">
-        <v>1081687860</v>
+        <v>1109881583</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -1872,31 +1872,31 @@
         <v>45657</v>
       </c>
       <c r="B37">
-        <v>187036954</v>
+        <v>183387190</v>
       </c>
       <c r="C37">
-        <v>7169359</v>
+        <v>12996121</v>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>47.2</v>
       </c>
       <c r="E37">
-        <v>9426152</v>
+        <v>8294454</v>
       </c>
       <c r="F37">
-        <v>38746284</v>
+        <v>34094426</v>
       </c>
       <c r="G37">
-        <v>110579</v>
+        <v>106855</v>
       </c>
       <c r="H37">
-        <v>1195051</v>
+        <v>1154812</v>
       </c>
       <c r="I37">
-        <v>3933530</v>
+        <v>1298825</v>
       </c>
       <c r="J37">
-        <v>80183</v>
+        <v>26476</v>
       </c>
       <c r="K37">
         <v>141.8</v>
@@ -1905,7 +1905,7 @@
         <v>0.9813</v>
       </c>
       <c r="M37">
-        <v>1096912349</v>
+        <v>1125502891</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -1913,31 +1913,31 @@
         <v>45688</v>
       </c>
       <c r="B38">
-        <v>192543627</v>
+        <v>193335402</v>
       </c>
       <c r="C38">
-        <v>7381519</v>
+        <v>13492494</v>
       </c>
       <c r="D38">
-        <v>26</v>
+        <v>47.5</v>
       </c>
       <c r="E38">
-        <v>10482539</v>
+        <v>9281230</v>
       </c>
       <c r="F38">
-        <v>45342343</v>
+        <v>40146066</v>
       </c>
       <c r="G38">
-        <v>4974929</v>
+        <v>4792974</v>
       </c>
       <c r="H38">
-        <v>54476966</v>
+        <v>52484507</v>
       </c>
       <c r="I38">
-        <v>2033262</v>
+        <v>659526</v>
       </c>
       <c r="J38">
-        <v>42130</v>
+        <v>13666</v>
       </c>
       <c r="K38">
         <v>90.8</v>
@@ -1946,7 +1946,7 @@
         <v>0.9798</v>
       </c>
       <c r="M38">
-        <v>1102819931</v>
+        <v>1131564452</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -1954,31 +1954,31 @@
         <v>45716</v>
       </c>
       <c r="B39">
-        <v>166999780</v>
+        <v>174390089</v>
       </c>
       <c r="C39">
-        <v>8403105</v>
+        <v>14850761</v>
       </c>
       <c r="D39">
-        <v>29.6</v>
+        <v>52.3</v>
       </c>
       <c r="E39">
-        <v>373795</v>
+        <v>330992</v>
       </c>
       <c r="F39">
-        <v>1635884</v>
+        <v>1448560</v>
       </c>
       <c r="G39">
-        <v>2995298</v>
+        <v>2889466</v>
       </c>
       <c r="H39">
-        <v>31539239</v>
+        <v>30424872</v>
       </c>
       <c r="I39">
-        <v>1388472</v>
+        <v>450938</v>
       </c>
       <c r="J39">
-        <v>25954</v>
+        <v>8429</v>
       </c>
       <c r="K39">
         <v>154.1</v>
@@ -1987,7 +1987,7 @@
         <v>0.9826</v>
       </c>
       <c r="M39">
-        <v>1091272662</v>
+        <v>1119716208</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -1995,31 +1995,31 @@
         <v>45747</v>
       </c>
       <c r="B40">
-        <v>163111903</v>
+        <v>167899653</v>
       </c>
       <c r="C40">
-        <v>4768888</v>
+        <v>8605867</v>
       </c>
       <c r="D40">
-        <v>16.1</v>
+        <v>29</v>
       </c>
       <c r="E40">
-        <v>12079608</v>
+        <v>10483899</v>
       </c>
       <c r="F40">
-        <v>52365273</v>
+        <v>45447853</v>
       </c>
       <c r="G40">
-        <v>52213</v>
+        <v>50070</v>
       </c>
       <c r="H40">
-        <v>604269</v>
+        <v>579472</v>
       </c>
       <c r="I40">
-        <v>1509105</v>
+        <v>494604</v>
       </c>
       <c r="J40">
-        <v>27956</v>
+        <v>9162</v>
       </c>
       <c r="K40">
         <v>133.7</v>
@@ -2028,7 +2028,7 @@
         <v>1.0245</v>
       </c>
       <c r="M40">
-        <v>1050869974</v>
+        <v>1078260442</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2036,31 +2036,31 @@
         <v>45777</v>
       </c>
       <c r="B41">
-        <v>141860910</v>
+        <v>147660943</v>
       </c>
       <c r="C41">
-        <v>266871</v>
+        <v>466962</v>
       </c>
       <c r="D41">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="E41">
-        <v>3916850</v>
+        <v>3335695</v>
       </c>
       <c r="F41">
-        <v>16541351</v>
+        <v>14087059</v>
       </c>
       <c r="G41">
-        <v>6628704</v>
+        <v>6401431</v>
       </c>
       <c r="H41">
-        <v>73089082</v>
+        <v>70583138</v>
       </c>
       <c r="I41">
-        <v>304265</v>
+        <v>101422</v>
       </c>
       <c r="J41">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="K41">
         <v>58.4</v>
@@ -2069,7 +2069,7 @@
         <v>1.0536</v>
       </c>
       <c r="M41">
-        <v>940368623</v>
+        <v>964878921</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2077,31 +2077,31 @@
         <v>45808</v>
       </c>
       <c r="B42">
-        <v>148123607</v>
+        <v>149611708</v>
       </c>
       <c r="C42">
-        <v>7611994</v>
+        <v>13486131</v>
       </c>
       <c r="D42">
-        <v>27.6</v>
+        <v>48.8</v>
       </c>
       <c r="E42">
-        <v>7519895</v>
+        <v>6624448</v>
       </c>
       <c r="F42">
-        <v>33993044</v>
+        <v>29945252</v>
       </c>
       <c r="G42">
-        <v>52966</v>
+        <v>50667</v>
       </c>
       <c r="H42">
-        <v>581132</v>
+        <v>555910</v>
       </c>
       <c r="I42">
-        <v>2162694</v>
+        <v>713089</v>
       </c>
       <c r="J42">
-        <v>43628</v>
+        <v>14385</v>
       </c>
       <c r="K42">
         <v>118.7</v>
@@ -2110,7 +2110,7 @@
         <v>1.0037</v>
       </c>
       <c r="M42">
-        <v>908407495</v>
+        <v>932084741</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2118,31 +2118,31 @@
         <v>45838</v>
       </c>
       <c r="B43">
-        <v>159305682</v>
+        <v>158064536</v>
       </c>
       <c r="C43">
-        <v>13439303</v>
+        <v>23373200</v>
       </c>
       <c r="D43">
-        <v>46.1</v>
+        <v>80.2</v>
       </c>
       <c r="E43">
-        <v>3567515</v>
+        <v>3124944</v>
       </c>
       <c r="F43">
-        <v>15469566</v>
+        <v>13550477</v>
       </c>
       <c r="G43">
-        <v>4245125</v>
+        <v>4097924</v>
       </c>
       <c r="H43">
-        <v>49706667</v>
+        <v>47983076</v>
       </c>
       <c r="I43">
-        <v>5947105</v>
+        <v>1970452</v>
       </c>
       <c r="J43">
-        <v>114837</v>
+        <v>38049</v>
       </c>
       <c r="K43">
         <v>122.8</v>
@@ -2151,7 +2151,7 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="M43">
-        <v>833324273</v>
+        <v>855044507</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2159,31 +2159,31 @@
         <v>45869</v>
       </c>
       <c r="B44">
-        <v>163147974</v>
+        <v>165369579</v>
       </c>
       <c r="C44">
-        <v>13226880</v>
+        <v>23114687</v>
       </c>
       <c r="D44">
-        <v>46.8</v>
+        <v>81.7</v>
       </c>
       <c r="E44">
-        <v>4626351</v>
+        <v>3964902</v>
       </c>
       <c r="F44">
-        <v>20326468</v>
+        <v>17420308</v>
       </c>
       <c r="G44">
-        <v>7174795</v>
+        <v>6936444</v>
       </c>
       <c r="H44">
-        <v>80203941</v>
+        <v>77539514</v>
       </c>
       <c r="I44">
-        <v>4019903</v>
+        <v>1332578</v>
       </c>
       <c r="J44">
-        <v>75471</v>
+        <v>25018</v>
       </c>
       <c r="K44">
         <v>144.2</v>
@@ -2192,7 +2192,7 @@
         <v>0.9664</v>
       </c>
       <c r="M44">
-        <v>888379339</v>
+        <v>911534560</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2200,31 +2200,31 @@
         <v>45900</v>
       </c>
       <c r="B45">
-        <v>137883501</v>
+        <v>140969130</v>
       </c>
       <c r="C45">
-        <v>183874</v>
+        <v>328953</v>
       </c>
       <c r="D45">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="E45">
-        <v>97439</v>
+        <v>80016</v>
       </c>
       <c r="F45">
-        <v>399457</v>
+        <v>328029</v>
       </c>
       <c r="G45">
-        <v>3754463</v>
+        <v>3582244</v>
       </c>
       <c r="H45">
-        <v>41758682</v>
+        <v>39843191</v>
       </c>
       <c r="I45">
-        <v>2329128</v>
+        <v>767555</v>
       </c>
       <c r="J45">
-        <v>42498</v>
+        <v>14005</v>
       </c>
       <c r="K45">
         <v>320.9</v>
@@ -2233,7 +2233,7 @@
         <v>0.9929</v>
       </c>
       <c r="M45">
-        <v>972582672</v>
+        <v>997932615</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2241,31 +2241,31 @@
         <v>45930</v>
       </c>
       <c r="B46">
-        <v>190294326</v>
+        <v>192936667</v>
       </c>
       <c r="C46">
-        <v>15826418</v>
+        <v>27525169</v>
       </c>
       <c r="D46">
-        <v>54.5</v>
+        <v>94.8</v>
       </c>
       <c r="E46">
-        <v>12841054</v>
+        <v>11298364</v>
       </c>
       <c r="F46">
-        <v>54542970</v>
+        <v>47990323</v>
       </c>
       <c r="G46">
-        <v>4288311</v>
+        <v>4135884</v>
       </c>
       <c r="H46">
-        <v>45574015</v>
+        <v>43954101</v>
       </c>
       <c r="I46">
-        <v>4004642</v>
+        <v>1319577</v>
       </c>
       <c r="J46">
-        <v>74057</v>
+        <v>24403</v>
       </c>
       <c r="K46">
         <v>32.2</v>
@@ -2274,7 +2274,7 @@
         <v>1.0016</v>
       </c>
       <c r="M46">
-        <v>1034026923</v>
+        <v>1060978384</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2282,31 +2282,31 @@
         <v>45961</v>
       </c>
       <c r="B47">
-        <v>180278828</v>
+        <v>190601769</v>
       </c>
       <c r="C47">
-        <v>12734804</v>
+        <v>22168590</v>
       </c>
       <c r="D47">
-        <v>43.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E47">
-        <v>4123954</v>
+        <v>3488441</v>
       </c>
       <c r="F47">
-        <v>16536582</v>
+        <v>13988247</v>
       </c>
       <c r="G47">
-        <v>3170412</v>
+        <v>3020042</v>
       </c>
       <c r="H47">
-        <v>32294475</v>
+        <v>30762778</v>
       </c>
       <c r="I47">
-        <v>1294106</v>
+        <v>422747</v>
       </c>
       <c r="J47">
-        <v>24490</v>
+        <v>8000</v>
       </c>
       <c r="K47">
         <v>136.1</v>
@@ -2315,7 +2315,7 @@
         <v>1.0065</v>
       </c>
       <c r="M47">
-        <v>1070746298</v>
+        <v>1098654834</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2323,31 +2323,31 @@
         <v>45991</v>
       </c>
       <c r="B48">
-        <v>196132986</v>
+        <v>203194545</v>
       </c>
       <c r="C48">
-        <v>11189555</v>
+        <v>19894649</v>
       </c>
       <c r="D48">
-        <v>37</v>
+        <v>65.7</v>
       </c>
       <c r="E48">
-        <v>7463932</v>
+        <v>6620018</v>
       </c>
       <c r="F48">
-        <v>32389692</v>
+        <v>28727530</v>
       </c>
       <c r="G48">
-        <v>119446</v>
+        <v>115340</v>
       </c>
       <c r="H48">
-        <v>1262211</v>
+        <v>1218826</v>
       </c>
       <c r="I48">
-        <v>2986366</v>
+        <v>988975</v>
       </c>
       <c r="J48">
-        <v>57223</v>
+        <v>18950</v>
       </c>
       <c r="K48">
         <v>76.40000000000001</v>
@@ -2356,7 +2356,7 @@
         <v>1.0203</v>
       </c>
       <c r="M48">
-        <v>1147533428</v>
+        <v>1177443387</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2364,31 +2364,31 @@
         <v>46022</v>
       </c>
       <c r="B49">
-        <v>174463012</v>
+        <v>183613753</v>
       </c>
       <c r="C49">
-        <v>11041667</v>
+        <v>19797994</v>
       </c>
       <c r="D49">
-        <v>36.1</v>
+        <v>64.7</v>
       </c>
       <c r="E49">
-        <v>995627</v>
+        <v>839673</v>
       </c>
       <c r="F49">
-        <v>4090828</v>
+        <v>3450046</v>
       </c>
       <c r="G49">
-        <v>52564</v>
+        <v>50045</v>
       </c>
       <c r="H49">
-        <v>566983</v>
+        <v>539815</v>
       </c>
       <c r="I49">
-        <v>2533258</v>
+        <v>831774</v>
       </c>
       <c r="J49">
-        <v>47059</v>
+        <v>15452</v>
       </c>
       <c r="K49">
         <v>337.5</v>
@@ -2397,7 +2397,7 @@
         <v>1.0102</v>
       </c>
       <c r="M49">
-        <v>1149022608</v>
+        <v>1178971381</v>
       </c>
     </row>
   </sheetData>
